--- a/tame_output/ON/bt/strategyON_20240211.xlsx
+++ b/tame_output/ON/bt/strategyON_20240211.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.0%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
     </row>
@@ -1405,11 +1405,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1869"/>
+  <dimension ref="A1:G1870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.404848910298174</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44548,6 +44548,29 @@
       </c>
       <c r="G1869" t="n">
         <v>4.468250891761635</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="2" t="n">
+        <v>45332</v>
+      </c>
+      <c r="B1870" t="n">
+        <v>3.426779760678667</v>
+      </c>
+      <c r="C1870" t="n">
+        <v>3.117162154822593</v>
+      </c>
+      <c r="D1870" t="n">
+        <v>1.615378395346084</v>
+      </c>
+      <c r="E1870" t="n">
+        <v>3.762957088647279</v>
+      </c>
+      <c r="F1870" t="n">
+        <v>2.25656622007763</v>
+      </c>
+      <c r="G1870" t="n">
+        <v>4.471101886869171</v>
       </c>
     </row>
   </sheetData>
